--- a/verification/cases/roundtrip/conditional_formatting/init.xlsx
+++ b/verification/cases/roundtrip/conditional_formatting/init.xlsx
@@ -1,17 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5E1B50F-DBDF-45AD-B32D-5A8B74D6250A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CF" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -48,7 +62,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -87,6 +101,18 @@
   <dxfs count="5">
     <dxf>
       <font>
+        <b/>
+        <i/>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i/>
         <u/>
@@ -97,18 +123,6 @@
         <b/>
         <i val="0"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i/>
-        <color rgb="FFFF0000"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -132,14 +146,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -177,7 +194,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -249,7 +266,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -422,14 +439,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>2</v>
       </c>
@@ -437,7 +454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -445,7 +462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5</v>
       </c>
@@ -453,7 +470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>-6</v>
       </c>
@@ -461,7 +478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -469,7 +486,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>-1</v>
       </c>
@@ -477,7 +494,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>0</v>
       </c>
@@ -485,13 +502,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>SUM(A1:A7)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -508,18 +525,18 @@
       <formula>-3</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9">
-    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
-      <formula>$A$8&gt;5</formula>
+  <conditionalFormatting sqref="B1:B7">
+    <cfRule type="cellIs" dxfId="2" priority="1" stopIfTrue="1" operator="lessThanOrEqual">
+      <formula>"AAA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" stopIfTrue="1" operator="between">
+      <formula>"A"</formula>
+      <formula>"AAA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B7">
-    <cfRule type="cellIs" dxfId="1" priority="1" stopIfTrue="1" operator="lessThanOrEqual">
-      <formula>"AAA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" stopIfTrue="1" operator="between">
-      <formula>"A"</formula>
-      <formula>"AAA"</formula>
+  <conditionalFormatting sqref="B9">
+    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+      <formula>$A$8&gt;5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -528,18 +545,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
